--- a/pensum/ok02/OK02_Viktige_begreper_Regneark_Kostnadsbegreper.xlsx
+++ b/pensum/ok02/OK02_Viktige_begreper_Regneark_Kostnadsbegreper.xlsx
@@ -1238,7 +1238,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1401,6 +1401,14 @@
     </xf>
     <xf numFmtId="167" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2112,8 +2120,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
+    <row ht="27" customHeight="true" r="35" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A35" t="s">
         <v>77</v>
       </c>
       <c r="B35" s="21" t="s">
@@ -2145,8 +2153,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="s">
+    <row ht="27" customHeight="true" r="38" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A38" t="s">
         <v>84</v>
       </c>
       <c r="B38" s="21" t="s">
@@ -2277,8 +2285,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+    <row ht="27" customHeight="true" r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A7" t="s">
         <v>105</v>
       </c>
       <c r="B7" s="24" t="n">
@@ -2414,8 +2422,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+    <row ht="27" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A16" t="s">
         <v>121</v>
       </c>
       <c r="B16" s="27" t="str">
@@ -2423,8 +2431,8 @@
         <v>OK — lager IB pluss alle kjøp minus lager UB er lik summen av varekostnadene</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+    <row ht="27" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A17" t="s">
         <v>122</v>
       </c>
       <c r="B17" s="27" t="str">
@@ -2782,8 +2790,8 @@
         <v>168</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
+    <row ht="27" customHeight="true" r="35" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A35" t="s">
         <v>169</v>
       </c>
       <c r="B35" s="27" t="str">
@@ -2849,8 +2857,8 @@
         <v>174</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+    <row ht="27" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A5" t="s">
         <v>175</v>
       </c>
       <c r="B5" s="24" t="n">
@@ -3162,8 +3170,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+    <row ht="27" customHeight="true" r="29" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A29" t="s">
         <v>198</v>
       </c>
       <c r="B29" s="27" t="str">
@@ -3508,8 +3516,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+    <row ht="27" customHeight="true" r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A26" t="s">
         <v>232</v>
       </c>
       <c r="B26" s="27" t="str">
@@ -3517,8 +3525,8 @@
         <v>OK — saldometoden avskriver mest i starten og minst mot slutten. Det er den store forskjellen mellom metodene</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+    <row ht="27" customHeight="true" r="27" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A27" t="s">
         <v>233</v>
       </c>
       <c r="B27" s="27" t="str">
@@ -3526,8 +3534,8 @@
         <v>OK — saldometoden bringer aldri bokført verdi helt ned i null. Den avskriver en prosent av restverdien hvert år</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+    <row ht="27" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A28" t="s">
         <v>234</v>
       </c>
       <c r="B28" s="27" t="str">
